--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_103_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_103_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>17</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>17</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
         <v>3</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>12</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3491,7 +3491,7 @@
         <v>22</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>109</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>33</v>
@@ -4488,16 +4488,16 @@
         <v>15</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>2</v>
@@ -4684,7 +4684,7 @@
         <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4880,16 +4880,16 @@
         <v>10</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X38" t="n">
         <v>7</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>1</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -5664,10 +5664,10 @@
         <v>7</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6059,13 +6059,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
         <v>2</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>98</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X48" t="n">
         <v>26</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_103_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_103_EL.xlsx
@@ -674,10 +674,10 @@
         <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>83.87</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1935,10 +1935,10 @@
         <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3307,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,10 +4500,10 @@
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>4</v>
       </c>
       <c r="X38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6068,14 +6068,14 @@
         <v>2</v>
       </c>
       <c r="X44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>9</v>
       </c>
       <c r="X48" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="Y48" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="AA48" t="n">
